--- a/Filtered/HCA_Florida_Woodmont_Hospital.xlsx
+++ b/Filtered/HCA_Florida_Woodmont_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1326,6 +1381,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1847,6 +1942,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1904,6 +2004,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2728,6 +2888,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2862,6 +3032,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2996,6 +3176,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3053,6 +3238,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3115,6 +3305,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3172,6 +3367,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3249,6 +3449,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3383,6 +3593,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3517,6 +3737,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3651,6 +3881,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3785,6 +4025,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3996,6 +4251,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4130,6 +4395,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4264,6 +4539,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4398,6 +4683,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +4827,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4589,6 +4889,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4666,6 +4971,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4723,6 +5033,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4800,6 +5115,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4857,6 +5177,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4934,6 +5259,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4991,6 +5321,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5068,6 +5403,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5145,6 +5485,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5202,6 +5547,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5279,6 +5629,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5336,6 +5691,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5398,6 +5758,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5455,6 +5820,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5532,6 +5902,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5589,6 +5964,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5666,6 +6046,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5723,6 +6108,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5800,6 +6190,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5857,6 +6252,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5934,6 +6334,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5991,6 +6396,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6068,6 +6478,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6125,6 +6540,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6202,6 +6622,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6259,6 +6684,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6336,6 +6766,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6393,6 +6828,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6470,6 +6910,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6527,6 +6972,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6589,6 +7039,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6646,6 +7101,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6723,6 +7183,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6780,6 +7245,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6857,6 +7327,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6914,6 +7389,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6991,6 +7471,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7048,6 +7533,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7125,6 +7615,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7182,6 +7677,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7259,6 +7759,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7316,6 +7821,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7393,6 +7903,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7450,6 +7965,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7527,6 +8047,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7584,6 +8109,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7661,6 +8191,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7718,6 +8253,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7795,6 +8335,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7852,6 +8397,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7914,6 +8464,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7971,6 +8526,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8048,6 +8608,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8105,6 +8670,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8182,6 +8752,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8259,6 +8834,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8316,6 +8896,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8393,6 +8978,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8470,6 +9060,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8527,6 +9122,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8604,6 +9204,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8661,6 +9266,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8738,6 +9348,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8815,6 +9430,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8872,6 +9492,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8949,6 +9574,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9006,6 +9636,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9083,6 +9718,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9160,6 +9800,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9217,6 +9862,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9294,6 +9944,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9351,6 +10006,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9428,6 +10088,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9485,6 +10150,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9562,6 +10232,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9619,6 +10294,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9681,6 +10361,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9738,6 +10423,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9800,6 +10490,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9862,6 +10557,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9919,6 +10619,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9996,6 +10701,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10053,6 +10763,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10130,6 +10845,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10187,6 +10907,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10264,6 +10989,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10321,6 +11051,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10398,6 +11133,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10455,6 +11195,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10532,6 +11277,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10589,6 +11339,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10666,6 +11421,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10723,6 +11483,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10800,6 +11565,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10857,6 +11627,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10934,6 +11709,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10991,6 +11771,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11068,6 +11853,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11125,6 +11915,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11202,6 +11997,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11259,6 +12059,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11336,6 +12141,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11393,6 +12203,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11470,6 +12285,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11527,6 +12347,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11604,6 +12429,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11661,6 +12491,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11738,6 +12573,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11795,6 +12635,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11872,6 +12717,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11929,6 +12779,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12006,6 +12861,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12083,6 +12943,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12140,6 +13005,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12202,6 +13072,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12259,6 +13134,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12321,6 +13201,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12378,6 +13263,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12440,6 +13330,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12497,6 +13392,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12574,6 +13474,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12631,6 +13536,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12708,6 +13618,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12765,6 +13680,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12842,6 +13762,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12899,6 +13824,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12976,6 +13906,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13033,6 +13968,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13110,6 +14050,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13167,6 +14112,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13244,6 +14194,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13301,6 +14256,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13378,6 +14338,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13435,6 +14400,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13512,6 +14482,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13569,6 +14544,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13646,6 +14626,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13703,6 +14688,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13780,6 +14770,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13837,6 +14832,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13914,6 +14914,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13971,6 +14976,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14048,6 +15058,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14105,6 +15120,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14182,6 +15202,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14239,6 +15264,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14316,6 +15346,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14373,6 +15408,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14450,6 +15490,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14507,6 +15552,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14584,6 +15634,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14641,6 +15696,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14718,6 +15778,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14775,6 +15840,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14852,6 +15922,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14909,6 +15984,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14986,6 +16066,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15043,6 +16128,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15120,6 +16210,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15177,6 +16272,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15254,6 +16354,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15311,6 +16416,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15388,6 +16498,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15445,6 +16560,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15522,6 +16642,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15579,6 +16704,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15656,6 +16786,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15713,6 +16848,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15790,6 +16930,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15847,6 +16992,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15924,6 +17074,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15981,6 +17136,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16058,6 +17218,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16115,6 +17280,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16177,6 +17347,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16234,6 +17409,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16311,6 +17491,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16368,6 +17553,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16445,6 +17635,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16502,6 +17697,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16579,6 +17779,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16636,6 +17841,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16713,6 +17923,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16770,6 +17985,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16847,6 +18067,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16904,6 +18129,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16981,6 +18211,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17058,6 +18293,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17115,6 +18355,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17192,6 +18437,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17249,6 +18499,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17326,6 +18581,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17383,6 +18643,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17460,6 +18725,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17517,6 +18787,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17594,6 +18869,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17651,6 +18931,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17728,6 +19013,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17785,6 +19075,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17862,6 +19157,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17919,6 +19219,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17996,6 +19301,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18053,6 +19363,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18130,6 +19445,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18187,6 +19507,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18264,6 +19589,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18321,6 +19651,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18398,6 +19733,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18455,6 +19795,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18532,6 +19877,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18589,6 +19939,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18666,6 +20021,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18723,6 +20083,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18800,6 +20165,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18857,6 +20227,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18934,6 +20309,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18991,6 +20371,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19068,6 +20453,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19125,6 +20515,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19202,6 +20597,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19259,6 +20659,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19336,6 +20741,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19393,6 +20803,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19470,6 +20885,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19527,6 +20947,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19604,6 +21029,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19661,6 +21091,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19738,6 +21173,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19795,6 +21235,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19872,6 +21317,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19929,6 +21379,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20006,6 +21461,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20063,6 +21523,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20140,6 +21605,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20197,6 +21667,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20274,6 +21749,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20331,6 +21811,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20408,6 +21893,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20485,6 +21975,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20542,6 +22037,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20619,6 +22119,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20676,6 +22181,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20753,6 +22263,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20810,6 +22325,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20887,6 +22407,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20944,6 +22469,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21021,6 +22551,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21078,6 +22613,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21155,6 +22695,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21232,6 +22777,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21289,6 +22839,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21366,6 +22921,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21423,6 +22983,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21500,6 +23065,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21577,6 +23147,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21634,6 +23209,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21711,6 +23291,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21768,6 +23353,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21845,6 +23435,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21902,6 +23497,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21979,6 +23579,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22036,6 +23641,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22113,6 +23723,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22170,6 +23785,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22247,6 +23867,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22304,6 +23929,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22376,6 +24006,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22433,6 +24068,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22510,6 +24150,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22587,6 +24232,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22644,6 +24294,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22706,6 +24361,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22763,6 +24423,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22840,6 +24505,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22897,6 +24567,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22974,6 +24649,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23031,6 +24711,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23108,6 +24793,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23165,6 +24855,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23227,6 +24922,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23284,6 +24984,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23361,6 +25066,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23418,6 +25128,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23480,6 +25195,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23537,6 +25257,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23614,6 +25339,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23671,6 +25401,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23748,6 +25483,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23805,6 +25545,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23882,6 +25627,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23939,6 +25689,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24001,6 +25756,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24058,6 +25818,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24135,6 +25900,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24192,6 +25962,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24269,6 +26044,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24326,6 +26106,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24403,6 +26188,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24460,6 +26250,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24537,6 +26332,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24594,6 +26394,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24671,6 +26476,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24728,6 +26538,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24805,6 +26620,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24862,6 +26682,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24924,6 +26749,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24981,6 +26811,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25058,6 +26893,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25115,6 +26955,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25192,6 +27037,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25249,6 +27099,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25326,6 +27181,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25383,6 +27243,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25460,6 +27325,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25517,6 +27387,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25594,6 +27469,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25651,6 +27531,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25713,6 +27598,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25770,6 +27660,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25847,6 +27742,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25904,6 +27804,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25981,6 +27886,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26038,6 +27948,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26115,6 +28030,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26172,6 +28092,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26249,6 +28174,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26306,6 +28236,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26383,6 +28318,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26440,6 +28380,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26517,6 +28462,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26574,6 +28524,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26651,6 +28606,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26708,6 +28668,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26785,6 +28750,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26842,6 +28812,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26904,6 +28879,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26966,6 +28946,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27028,6 +29013,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27085,6 +29075,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27162,6 +29157,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27219,6 +29219,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27281,6 +29286,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27343,6 +29353,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27405,6 +29420,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27467,6 +29487,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27529,6 +29554,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27591,6 +29621,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27648,6 +29683,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27725,6 +29765,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27782,6 +29827,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27859,6 +29909,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27916,6 +29971,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27978,6 +30038,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28040,6 +30105,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28097,6 +30167,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28174,6 +30249,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28231,6 +30311,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28308,6 +30393,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28365,6 +30455,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28427,6 +30522,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28484,6 +30584,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28546,6 +30651,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28608,6 +30718,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28665,6 +30780,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28727,6 +30847,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28789,6 +30914,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28851,6 +30981,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28908,6 +31043,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28985,6 +31125,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29042,6 +31187,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29104,6 +31254,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29166,6 +31321,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29228,6 +31388,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29285,6 +31450,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29347,6 +31517,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29409,6 +31584,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29471,6 +31651,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29528,6 +31713,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29605,6 +31795,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29662,6 +31857,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29724,6 +31924,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29781,6 +31986,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29858,6 +32068,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29915,6 +32130,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29977,6 +32197,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30039,6 +32264,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30101,6 +32331,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30158,6 +32393,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30235,6 +32475,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30292,6 +32537,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30369,6 +32619,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30426,6 +32681,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30488,6 +32748,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30550,6 +32815,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30612,6 +32882,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30669,6 +32944,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30731,6 +33011,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30793,6 +33078,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30855,6 +33145,11 @@
           <t>COCUH</t>
         </is>
       </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30910,6 +33205,11 @@
       <c r="K461" t="inlineStr">
         <is>
           <t>COCUH</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
